--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importContractSign.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importContractSign.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\25757\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-pm\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA857082-9178-40DD-89FD-E987681E397A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09BED4DA-0761-48D9-8261-565B85E7D87B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023-07-05" sheetId="1" r:id="rId1"/>
@@ -407,15 +407,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="2" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
-    <col min="4" max="4" width="16.5546875" customWidth="1"/>
-    <col min="5" max="5" width="24.5546875" customWidth="1"/>
+    <col min="1" max="2" width="16.625" customWidth="1"/>
+    <col min="3" max="3" width="15.125" customWidth="1"/>
+    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="5" max="5" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -432,7 +432,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
@@ -441,6 +441,13 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576" xr:uid="{BD903BF0-E604-4916-A283-03C5CE01BE64}">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>